--- a/tables/datas/common/#RoleInitConfig-角色初始配置表.xlsx
+++ b/tables/datas/common/#RoleInitConfig-角色初始配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,6 +429,11 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>##</t>
         </is>
       </c>
@@ -444,12 +449,12 @@
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>配置ID</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -464,12 +469,12 @@
           <t>string</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>初始道具</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1001:1,1002:10,2001:100</t>
         </is>
@@ -486,12 +491,12 @@
           <t>string</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>初始任务</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1001,1002</t>
         </is>
@@ -508,12 +513,12 @@
           <t>int</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>初始引导步骤</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1001</v>
       </c>
     </row>
